--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>

--- a/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/uy/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación por egreso»: ponés tus fechas y tu sueldo, y te dice el aguinaldo, la licencia, el salario vacacional y, si te despidieron, la indemnización.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de Uruguay</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2142,7 +2142,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="26">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>83</v>
